--- a/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_4.xlsx
+++ b/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,170 +595,74 @@
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>echo4_sora_return</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ソラ:「三秒──二回返ってきた。間。三回返ってきた」</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sora: 'Three seconds—two claps. Pause. Three claps.'</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Sora: 'Three seconds—two claps. Pause. Three claps.'</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>echo4_sora_shock</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ソラ:「パターンを送ったら、パターンが返ってきた」</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sora: 'I sent a pattern. A pattern came back.'</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Sora: 'I sent a pattern. A pattern came back.'</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>echo4_sora_verdict</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ソラ:「これは反射じゃない。応答だ。何かがこちらを認識して返事をしている」</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Sora: 'This isn't reflection. It's response. Something is hearing us and replying.'</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Sora: 'This isn't reflection. It's response. Something is hearing us and replying.'</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>echo4_mina_quiet</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ミナ:「……」</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Mina: '...'</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Mina: '...'</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>echo4_sora_confirm</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ソラ:「ミナ。聞いたよな？」</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Sora: 'Mina. You heard that, right?'</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Sora: 'Mina. You heard that, right?'</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>echo4_mina_heard</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ミナ:「……聞いた」</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Mina: '...I heard it.'</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Mina: '...I heard it.'</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_pattern");</t>
         </is>
       </c>
     </row>
@@ -770,86 +674,254 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>echo4_sora_conclusion</t>
+          <t>echo4_sora_return</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ソラ:「ここに何かいる。知性がある。伝えようとしてる」</t>
+          <t>ソラ:「三秒──二回返ってきた。間。三回返ってきた」</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Sora: 'Something is here. It's intelligent. And it's trying to talk.'</t>
+          <t>Sora: 'Three seconds—two claps. Pause. Three claps.'</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
+          <t>Sora: 'Three seconds—two claps. Pause. Three claps.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>echo4_sora_shock</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ソラ:「パターンを送ったら、パターンが返ってきた」</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Sora: 'I sent a pattern. A pattern came back.'</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Sora: 'I sent a pattern. A pattern came back.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>echo4_sora_verdict</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ソラ:「これは反射じゃない。応答だ。何かがこちらを認識して返事をしている」</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Sora: 'This isn't reflection. It's response. Something is hearing us and replying.'</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Sora: 'This isn't reflection. It's response. Something is hearing us and replying.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>echo4_mina_quiet</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ミナ:「……」</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Mina: '...'</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Mina: '...'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>echo4_sora_confirm</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ソラ:「ミナ。聞いたよな？」</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Sora: 'Mina. You heard that, right?'</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Sora: 'Mina. You heard that, right?'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>echo4_mina_heard</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ミナ:「……聞いた」</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mina: '...I heard it.'</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Mina: '...I heard it.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>echo4_sora_conclusion</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ソラ:「ここに何かいる。知性がある。伝えようとしてる」</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Sora: 'Something is here. It's intelligent. And it's trying to talk.'</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Sora: 'Something is here. It's intelligent. And it's trying to talk.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="E22" t="inlineStr">
+    <row r="28">
+      <c r="E28" t="inlineStr">
         <is>
           <t>setFlag</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>chitsii.elinikki.quest.state.echo_experiment,4</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="E23" t="inlineStr">
+    <row r="29">
+      <c r="E29" t="inlineStr">
         <is>
           <t>setFlag</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>chitsii.elinikki.quest.event.trace_echo,1</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="E24" t="inlineStr">
+    <row r="30">
+      <c r="E30" t="inlineStr">
         <is>
           <t>fadeOut</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>0.3,black</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="E25" t="inlineStr">
+    <row r="31">
+      <c r="E31" t="inlineStr">
         <is>
           <t>setBG</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="E26" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="E32" t="inlineStr">
         <is>
           <t>end</t>
         </is>
